--- a/ig/DM-MARS-2026/CodeSystem-ActMood-supplement-fr.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-ActMood-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ActMood|3.0.0</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ActMood|4.0.0</t>
   </si>
   <si>
     <t>Count</t>

--- a/ig/DM-MARS-2026/CodeSystem-ActMood-supplement-fr.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-ActMood-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-ActMood|4.0.0</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ActMood|2018-08-12</t>
   </si>
   <si>
     <t>Count</t>
